--- a/docs/03_Roadmap.xlsx
+++ b/docs/03_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danil\Desktop\Z_messenger\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFADCB3-C02A-4AEB-A17F-63AAACA4D34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED83E05A-230A-419B-8F60-7C4201E02B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,9 +136,15 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,17 +167,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -463,193 +473,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4"/>
+      <c r="E2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4"/>
+      <c r="E3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="6" t="s">
         <v>29</v>
       </c>
     </row>

--- a/docs/03_Roadmap.xlsx
+++ b/docs/03_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danil\Desktop\Z_messenger\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED83E05A-230A-419B-8F60-7C4201E02B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DEDE34-45FF-443B-B39B-3C6684F41EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,7 +467,7 @@
   <cols>
     <col min="2" max="2" width="32.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.44140625" customWidth="1"/>
-    <col min="4" max="4" width="125.33203125" customWidth="1"/>
+    <col min="4" max="4" width="128.6640625" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
